--- a/bench/corpus/clean-10.xlsx
+++ b/bench/corpus/clean-10.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyank\Desktop\後藤さんのclaude\ai-builders-2026\gridlint\bench\corpus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DF3D6D1-F811-4B75-933B-FB7D4312659D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C842D8FC-EAF8-48C9-9340-8C79CB573666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1943D774-89D8-4FD8-9FA0-9A38447797F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{89E5FC0A-34D8-430D-A6E6-0EB6C90D4D43}"/>
   </bookViews>
   <sheets>
-    <sheet name="Model" sheetId="2" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="1" r:id="rId2"/>
+    <sheet name="Model" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,19 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>Assumption</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Headcount</t>
-  </si>
-  <si>
-    <t>Cash on hand</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Plan</t>
   </si>
@@ -69,58 +56,61 @@
     <t>Mar</t>
   </si>
   <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
     <t>REVENUE</t>
   </si>
   <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>Software tools</t>
+  </si>
+  <si>
+    <t>Total revenue</t>
+  </si>
+  <si>
+    <t>COST OF SALES</t>
+  </si>
+  <si>
     <t>Cloud hosting</t>
   </si>
   <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>Total revenue</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>North</t>
-  </si>
-  <si>
-    <t>South</t>
-  </si>
-  <si>
-    <t>East</t>
-  </si>
-  <si>
-    <t>West</t>
-  </si>
-  <si>
-    <t>Weighted first month</t>
+    <t>Advertising</t>
+  </si>
+  <si>
+    <t>Agency fees</t>
+  </si>
+  <si>
+    <t>Total cost of sales</t>
+  </si>
+  <si>
+    <t>OPERATING COSTS</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Contractors</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Total operating costs</t>
+  </si>
+  <si>
+    <t>Grand total</t>
+  </si>
+  <si>
+    <t>Share of first month</t>
   </si>
   <si>
     <t>Full year</t>
   </si>
   <si>
-    <t>Per head</t>
-  </si>
-  <si>
-    <t>Months of cash</t>
+    <t>helper</t>
   </si>
 </sst>
 </file>
@@ -128,8 +118,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="179" formatCode="\$#,##0"/>
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
+    <numFmt numFmtId="180" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -513,281 +503,329 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E7C07AE-563B-42B4-81BA-54B46C788820}">
-  <dimension ref="A1:H20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109EF6CB-1EFA-41C9-9050-326C68E96C88}">
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.625" customWidth="1"/>
-    <col min="3" max="8" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>314000</v>
-      </c>
-      <c r="D6" s="1">
-        <f>C6*(1+$B$6)</f>
-        <v>319652</v>
-      </c>
-      <c r="E6" s="1">
-        <f>D6*(1+$B$6)</f>
-        <v>325405.73600000003</v>
-      </c>
-      <c r="F6" s="1">
-        <f>E6*(1+$B$6)</f>
-        <v>331263.03924800002</v>
-      </c>
-      <c r="G6" s="1">
-        <f>F6*(1+$B$6)</f>
-        <v>337225.77395446401</v>
-      </c>
-      <c r="H6" s="1">
-        <f>G6*(1+$B$6)</f>
-        <v>343295.83788564435</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2">
-        <v>3.1E-2</v>
-      </c>
-      <c r="C7" s="1">
-        <v>395000</v>
-      </c>
-      <c r="D7" s="1">
-        <f>C7*(1+$B$7)</f>
-        <v>407244.99999999994</v>
-      </c>
-      <c r="E7" s="1">
-        <f>D7*(1+$B$7)</f>
-        <v>419869.59499999991</v>
-      </c>
-      <c r="F7" s="1">
-        <f>E7*(1+$B$7)</f>
-        <v>432885.55244499986</v>
-      </c>
-      <c r="G7" s="1">
-        <f>F7*(1+$B$7)</f>
-        <v>446305.00457079482</v>
-      </c>
-      <c r="H7" s="1">
-        <f>G7*(1+$B$7)</f>
-        <v>460140.45971248939</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2">
-        <v>-1.4999999999999999E-2</v>
-      </c>
-      <c r="C8" s="1">
-        <v>388000</v>
-      </c>
-      <c r="D8" s="1">
-        <f>C8*(1+$B$8)</f>
-        <v>382180</v>
-      </c>
-      <c r="E8" s="1">
-        <f>D8*(1+$B$8)</f>
-        <v>376447.3</v>
-      </c>
-      <c r="F8" s="1">
-        <f>E8*(1+$B$8)</f>
-        <v>370800.59049999999</v>
-      </c>
-      <c r="G8" s="1">
-        <f>F8*(1+$B$8)</f>
-        <v>365238.58164250001</v>
-      </c>
-      <c r="H8" s="1">
-        <f>G8*(1+$B$8)</f>
-        <v>359760.0029178625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1">
-        <f>SUM(C6:C8)</f>
-        <v>1097000</v>
-      </c>
-      <c r="D9" s="1">
-        <f>SUM(D6:D8)</f>
-        <v>1109077</v>
-      </c>
-      <c r="E9" s="1">
-        <f>SUM(E6:E8)</f>
-        <v>1121722.6310000001</v>
-      </c>
-      <c r="F9" s="1">
-        <f>SUM(F6:F8)</f>
-        <v>1134949.1821929999</v>
-      </c>
-      <c r="G9" s="1">
-        <f>SUM(G6:G8)</f>
-        <v>1148769.360167759</v>
-      </c>
-      <c r="H9" s="1">
-        <f>SUM(H6:H8)</f>
-        <v>1163196.3005159963</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="1">
-        <f>ROUND(C9*VLOOKUP("East",A12:B15,2,FALSE),0)</f>
-        <v>548500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="1">
-        <f>SUM(C9:H9)</f>
-        <v>6774714.4738767557</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="1">
-        <f>ROUND(C18/Assumptions!B2,0)</f>
-        <v>356564</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20">
-        <f>ROUND(Assumptions!B3/AVERAGE(C9:H9),1)</f>
-        <v>4.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4CF62A6-7FCE-4143-99AB-04AED7DFE29D}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="C6" s="2">
+        <v>118000</v>
+      </c>
+      <c r="D6" s="2">
+        <f>C6*(1+$B$6)</f>
+        <v>128266</v>
+      </c>
+      <c r="E6" s="2">
+        <f>D6*(1+$B$6)</f>
+        <v>139425.14199999999</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="C7" s="2">
+        <v>258000</v>
+      </c>
+      <c r="D7" s="2">
+        <f>C7*(1+$B$7)</f>
+        <v>268320</v>
+      </c>
+      <c r="E7" s="2">
+        <f>D7*(1+$B$7)</f>
+        <v>279052.79999999999</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="C8" s="2">
+        <v>193000</v>
+      </c>
+      <c r="D8" s="2">
+        <f>C8*(1+$B$8)</f>
+        <v>207668</v>
+      </c>
+      <c r="E8" s="2">
+        <f>D8*(1+$B$8)</f>
+        <v>223450.76800000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2">
+        <f>SUM(C6:C8)</f>
+        <v>569000</v>
+      </c>
+      <c r="D9" s="2">
+        <f>SUM(D6:D8)</f>
+        <v>604254</v>
+      </c>
+      <c r="E9" s="2">
+        <f>SUM(E6:E8)</f>
+        <v>641928.71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>264000</v>
+      </c>
+      <c r="D12" s="2">
+        <f>C12*(1+$B$12)</f>
+        <v>269544</v>
+      </c>
+      <c r="E12" s="2">
+        <f>D12*(1+$B$12)</f>
+        <v>275204.424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>338000</v>
+      </c>
+      <c r="D13" s="2">
+        <f>C13*(1+$B$13)</f>
+        <v>354562</v>
+      </c>
+      <c r="E13" s="2">
+        <f>D13*(1+$B$13)</f>
+        <v>371935.538</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C14" s="2">
+        <v>245000</v>
+      </c>
+      <c r="D14" s="2">
+        <f>C14*(1+$B$14)</f>
+        <v>259700</v>
+      </c>
+      <c r="E14" s="2">
+        <f>D14*(1+$B$14)</f>
+        <v>275282</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2">
+        <f>SUM(C12:C14)</f>
+        <v>847000</v>
+      </c>
+      <c r="D15" s="2">
+        <f>SUM(D12:D14)</f>
+        <v>883806</v>
+      </c>
+      <c r="E15" s="2">
+        <f>SUM(E12:E14)</f>
+        <v>922421.96200000006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="C18" s="2">
+        <v>248000</v>
+      </c>
+      <c r="D18" s="2">
+        <f>C18*(1+$B$18)</f>
+        <v>267840</v>
+      </c>
+      <c r="E18" s="2">
+        <f>D18*(1+$B$18)</f>
+        <v>289267.20000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="C19" s="2">
+        <v>86000</v>
+      </c>
+      <c r="D19" s="2">
+        <f>C19*(1+$B$19)</f>
+        <v>87117.999999999985</v>
+      </c>
+      <c r="E19" s="2">
+        <f>D19*(1+$B$19)</f>
+        <v>88250.533999999971</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+      <c r="C20" s="2">
+        <v>24000</v>
+      </c>
+      <c r="D20" s="2">
+        <f>C20*(1+$B$20)</f>
+        <v>23688</v>
+      </c>
+      <c r="E20" s="2">
+        <f>D20*(1+$B$20)</f>
+        <v>23380.056</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
-        <v>4700000</v>
+      <c r="C21" s="2">
+        <f>SUM(C18:C20)</f>
+        <v>358000</v>
+      </c>
+      <c r="D21" s="2">
+        <f>SUM(D18:D20)</f>
+        <v>378646</v>
+      </c>
+      <c r="E21" s="2">
+        <f>SUM(E18:E20)</f>
+        <v>400897.79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2">
+        <f>SUM(C9,C15,C21)</f>
+        <v>1774000</v>
+      </c>
+      <c r="D23" s="2">
+        <f>SUM(D9,D15,D21)</f>
+        <v>1866706</v>
+      </c>
+      <c r="E23" s="2">
+        <f>SUM(E9,E15,E21)</f>
+        <v>1965248.4620000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1">
+        <f>C23/$C$23</f>
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <f>D23/$C$23</f>
+        <v>1.0522581736189403</v>
+      </c>
+      <c r="E24" s="1">
+        <f>E23/$C$23</f>
+        <v>1.1078063483652762</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="2">
+        <f>SUM(C23:E23)</f>
+        <v>5605954.4620000003</v>
       </c>
     </row>
   </sheetData>
